--- a/measurements/25/Filled_2D_sections/sagittal/week25_sagittal_Batch_Allmarks.xlsx
+++ b/measurements/25/Filled_2D_sections/sagittal/week25_sagittal_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:W27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,52 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,17 +546,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4.954491374182035</v>
+        <v>1888.548752834467</v>
       </c>
       <c r="D2" t="n">
-        <v>11.01678971546452</v>
+        <v>215.089703968593</v>
       </c>
       <c r="E2" t="n">
-        <v>9.968727228118153</v>
+        <v>194.6275315965925</v>
       </c>
       <c r="F2" t="n">
         <v>1.105135035131683</v>
@@ -525,24 +565,45 @@
         <v>0.5129780956203315</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>0.817358993902439</v>
+        <v>1.795014880952381</v>
       </c>
       <c r="J2" t="n">
-        <v>0.817358993902439</v>
+        <v>15.95796130952381</v>
       </c>
       <c r="K2" t="n">
-        <v>0.817358993902439</v>
-      </c>
-      <c r="N2" t="inlineStr">
+        <v>8.560887896825397</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>15.95796130952381</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>7.9296875</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.795014880952381</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>5.042088042831648</v>
+      <c r="W2" s="2" t="n">
+        <v>1921.938775510204</v>
       </c>
     </row>
     <row r="3">
@@ -553,17 +614,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.954491374182035</v>
+        <v>1888.548752834467</v>
       </c>
       <c r="D3" t="n">
-        <v>11.01678971546452</v>
+        <v>215.089703968593</v>
       </c>
       <c r="E3" t="n">
-        <v>9.968727228118153</v>
+        <v>194.6275315965925</v>
       </c>
       <c r="F3" t="n">
         <v>1.105135035131683</v>
@@ -572,24 +633,45 @@
         <v>0.5129780956203315</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>0.817358993902439</v>
+        <v>1.795014880952381</v>
       </c>
       <c r="J3" t="n">
-        <v>0.817358993902439</v>
+        <v>15.95796130952381</v>
       </c>
       <c r="K3" t="n">
-        <v>0.817358993902439</v>
-      </c>
-      <c r="N3" t="inlineStr">
+        <v>8.560887896825397</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>15.95796130952381</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>7.9296875</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.795014880952381</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>10.06630053680118</v>
+      <c r="W3" s="2" t="n">
+        <v>196.5325342899277</v>
       </c>
     </row>
     <row r="4">
@@ -600,17 +682,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5.007733491969066</v>
+        <v>1908.843537414966</v>
       </c>
       <c r="D4" t="n">
-        <v>11.09169382002296</v>
+        <v>216.5521174385434</v>
       </c>
       <c r="E4" t="n">
-        <v>10.0317951964169</v>
+        <v>195.8588585967109</v>
       </c>
       <c r="F4" t="n">
         <v>1.105653933603491</v>
@@ -619,24 +701,45 @@
         <v>0.5115114112263485</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8192644817073171</v>
+        <v>1.532738095238095</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8192644817073171</v>
+        <v>15.99516369047619</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8192644817073171</v>
-      </c>
-      <c r="N4" t="inlineStr">
+        <v>8.604290674603174</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>15.99516369047619</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>8.284970238095237</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.532738095238095</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>9.582916797951954</v>
+      <c r="W4" s="2" t="n">
+        <v>187.0950422457286</v>
       </c>
     </row>
     <row r="5">
@@ -647,42 +750,63 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.053837001784652</v>
+        <v>1926.417233560091</v>
       </c>
       <c r="D5" t="n">
-        <v>11.20354227321904</v>
+        <v>218.7358253342765</v>
       </c>
       <c r="E5" t="n">
-        <v>9.879535675048828</v>
+        <v>192.8861727033342</v>
       </c>
       <c r="F5" t="n">
         <v>1.134015063229545</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5059648890677835</v>
+        <v>0.5059648890677836</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8090701219512195</v>
+        <v>1.290922619047619</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8090701219512195</v>
+        <v>15.79613095238095</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8090701219512195</v>
-      </c>
-      <c r="N5" t="inlineStr">
+        <v>8.349454365079366</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>15.79613095238095</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>7.961309523809524</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.290922619047619</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="W5" s="2" t="n">
         <v>1.049308870627409</v>
       </c>
     </row>
@@ -694,43 +818,64 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5.053837001784652</v>
+        <v>1926.417233560091</v>
       </c>
       <c r="D6" t="n">
-        <v>11.20354227321904</v>
+        <v>218.7358253342765</v>
       </c>
       <c r="E6" t="n">
-        <v>9.879535675048828</v>
+        <v>192.8861727033342</v>
       </c>
       <c r="F6" t="n">
         <v>1.134015063229545</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5059648890677835</v>
+        <v>0.5059648890677836</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8090701219512195</v>
+        <v>1.290922619047619</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8090701219512195</v>
+        <v>15.79613095238095</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8090701219512195</v>
-      </c>
-      <c r="N6" t="inlineStr">
+        <v>8.349454365079366</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>15.79613095238095</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>7.961309523809524</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.290922619047619</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
-        <v>0.63451665261748</v>
+      <c r="W6" s="2" t="n">
+        <v>0.6345166526174801</v>
       </c>
     </row>
     <row r="7">
@@ -741,43 +886,64 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5.11511005353956</v>
+        <v>1949.773242630385</v>
       </c>
       <c r="D7" t="n">
-        <v>11.39866421571592</v>
+        <v>222.5453489735013</v>
       </c>
       <c r="E7" t="n">
-        <v>9.741563616729364</v>
+        <v>190.1924325170971</v>
       </c>
       <c r="F7" t="n">
         <v>1.170106223619049</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4947171039462961</v>
+        <v>0.494717103946296</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7741044207317074</v>
+        <v>1.311383928571429</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7741044207317074</v>
+        <v>15.11346726190476</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7741044207317074</v>
-      </c>
-      <c r="N7" t="inlineStr">
+        <v>8.077256944444445</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>15.11346726190476</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>7.806919642857142</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.311383928571429</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>0.3</v>
+      <c r="W7" s="2" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="8">
@@ -788,34 +954,61 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5.24330755502677</v>
+        <v>1998.639455782313</v>
       </c>
       <c r="D8" t="n">
-        <v>9.991384113707193</v>
+        <v>195.0698803152357</v>
       </c>
       <c r="E8" t="n">
-        <v>9.712988667371796</v>
+        <v>189.6345406486874</v>
       </c>
       <c r="F8" t="n">
         <v>1.028662181731004</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6600303190875866</v>
+        <v>0.6600303190875865</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5.15625</v>
+      </c>
+      <c r="J8" t="n">
+        <v>7.81063988095238</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6.48344494047619</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>7.81063988095238</v>
+      </c>
+      <c r="P8" t="n">
+        <v>5.15625</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.8077045223577236</v>
+      <c r="W8" s="2" t="n">
+        <v>2.750837053571428</v>
       </c>
     </row>
     <row r="9">
@@ -826,34 +1019,61 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5.21772754312909</v>
+        <v>1988.888888888889</v>
       </c>
       <c r="D9" t="n">
-        <v>9.922398093270093</v>
+        <v>193.7230103924161</v>
       </c>
       <c r="E9" t="n">
-        <v>9.672577602107351</v>
+        <v>188.8455627078102</v>
       </c>
       <c r="F9" t="n">
         <v>1.025827706061341</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6659750622595643</v>
+        <v>0.6659750622595644</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.799107142857142</v>
+      </c>
+      <c r="J9" t="n">
+        <v>7.745535714285714</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6.272321428571428</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>7.745535714285714</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4.799107142857142</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>0.8077045223577236</v>
+      <c r="W9" s="2" t="n">
+        <v>10.05738467261905</v>
       </c>
     </row>
     <row r="10">
@@ -864,34 +1084,61 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5.21772754312909</v>
+        <v>1988.888888888889</v>
       </c>
       <c r="D10" t="n">
-        <v>9.922398093270093</v>
+        <v>193.7230103924161</v>
       </c>
       <c r="E10" t="n">
-        <v>9.672577602107351</v>
+        <v>188.8455627078102</v>
       </c>
       <c r="F10" t="n">
         <v>1.025827706061341</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6659750622595643</v>
+        <v>0.6659750622595644</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.799107142857142</v>
+      </c>
+      <c r="J10" t="n">
+        <v>7.745535714285714</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.272321428571428</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>7.745535714285714</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4.799107142857142</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.8077045223577236</v>
+      <c r="W10" s="2" t="n">
+        <v>6.338402157738095</v>
       </c>
     </row>
     <row r="11">
@@ -902,17 +1149,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5.198988697204046</v>
+        <v>1981.746031746032</v>
       </c>
       <c r="D11" t="n">
-        <v>9.847494009064466</v>
+        <v>192.26059731983</v>
       </c>
       <c r="E11" t="n">
-        <v>9.603591590392881</v>
+        <v>187.4986929552896</v>
       </c>
       <c r="F11" t="n">
         <v>1.025397000317629</v>
@@ -921,7 +1168,42 @@
         <v>0.6737166597077002</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.241071428571428</v>
+      </c>
+      <c r="J11" t="n">
+        <v>7.71391369047619</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.977492559523808</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>7.71391369047619</v>
+      </c>
+      <c r="P11" t="n">
+        <v>4.241071428571428</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="12">
@@ -932,26 +1214,61 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5.157346817370613</v>
+        <v>1965.873015873016</v>
       </c>
       <c r="D12" t="n">
-        <v>9.738096911732743</v>
+        <v>190.1247492290678</v>
       </c>
       <c r="E12" t="n">
-        <v>9.563180516405804</v>
+        <v>186.7097148441133</v>
       </c>
       <c r="F12" t="n">
         <v>1.018290608969147</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6834205239019531</v>
+        <v>0.6834205239019528</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.528645833333333</v>
+      </c>
+      <c r="J12" t="n">
+        <v>7.516741071428571</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5.522693452380953</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>7.516741071428571</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.528645833333333</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="n">
+        <v>15.76946924603175</v>
       </c>
     </row>
     <row r="13">
@@ -962,26 +1279,61 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5.120166567519334</v>
+        <v>1951.700680272109</v>
       </c>
       <c r="D13" t="n">
-        <v>9.686865079693678</v>
+        <v>189.1245086987813</v>
       </c>
       <c r="E13" t="n">
-        <v>9.494194481430984</v>
+        <v>185.362844637462</v>
       </c>
       <c r="F13" t="n">
         <v>1.020293517121387</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6856894253258818</v>
+        <v>0.6856894253258821</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.642113095238095</v>
+      </c>
+      <c r="J13" t="n">
+        <v>7.04985119047619</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.345982142857142</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>7.04985119047619</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.642113095238095</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="n">
+        <v>1.35</v>
       </c>
     </row>
     <row r="14">
@@ -992,26 +1344,61 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5.120166567519334</v>
+        <v>1951.700680272109</v>
       </c>
       <c r="D14" t="n">
-        <v>9.686865079693678</v>
+        <v>189.1245086987813</v>
       </c>
       <c r="E14" t="n">
-        <v>9.494194481430984</v>
+        <v>185.362844637462</v>
       </c>
       <c r="F14" t="n">
         <v>1.020293517121387</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6856894253258818</v>
+        <v>0.6856894253258821</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.642113095238095</v>
+      </c>
+      <c r="J14" t="n">
+        <v>7.04985119047619</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5.345982142857142</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>7.04985119047619</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3.642113095238095</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="n">
+        <v>7.720238095238095</v>
       </c>
     </row>
     <row r="15">
@@ -1022,26 +1409,61 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5.072278405710887</v>
+        <v>1933.44671201814</v>
       </c>
       <c r="D15" t="n">
-        <v>9.531138856236527</v>
+        <v>186.0841395741417</v>
       </c>
       <c r="E15" t="n">
-        <v>9.468070885030235</v>
+        <v>184.852812517257</v>
       </c>
       <c r="F15" t="n">
         <v>1.006661121570816</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7016545625566069</v>
+        <v>0.7016545625566067</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.126860119047619</v>
+      </c>
+      <c r="J15" t="n">
+        <v>6.936383928571428</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.031622023809524</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>6.936383928571428</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>3.126860119047619</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="n">
+        <v>4.258343962585033</v>
       </c>
     </row>
     <row r="16">
@@ -1052,26 +1474,61 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5.01279000594884</v>
+        <v>1910.770975056689</v>
       </c>
       <c r="D16" t="n">
-        <v>9.453783424889169</v>
+        <v>184.5738668668838</v>
       </c>
       <c r="E16" t="n">
-        <v>9.405002934176748</v>
+        <v>183.6214858577365</v>
       </c>
       <c r="F16" t="n">
         <v>1.005186653428375</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7048197707832451</v>
+        <v>0.704819770783245</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.661830357142857</v>
+      </c>
+      <c r="J16" t="n">
+        <v>7.122395833333333</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.892113095238095</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>7.122395833333333</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.661830357142857</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="n">
+        <v>0.65</v>
       </c>
     </row>
     <row r="17">
@@ -1082,26 +1539,61 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4.944080904223677</v>
+        <v>1884.580498866213</v>
       </c>
       <c r="D17" t="n">
-        <v>9.370509883252586</v>
+        <v>182.9480501015981</v>
       </c>
       <c r="E17" t="n">
-        <v>9.295605793231871</v>
+        <v>181.4856369154794</v>
       </c>
       <c r="F17" t="n">
         <v>1.008058010600584</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7075693086092922</v>
+        <v>0.7075693086092923</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.317708333333333</v>
+      </c>
+      <c r="J17" t="n">
+        <v>7.468377976190475</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.893043154761904</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>7.468377976190475</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.317708333333333</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="n">
+        <v>1.939102564102564</v>
       </c>
     </row>
     <row r="18">
@@ -1112,25 +1604,60 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4.944080904223677</v>
+        <v>1884.580498866213</v>
       </c>
       <c r="D18" t="n">
-        <v>9.370509883252586</v>
+        <v>182.9480501015981</v>
       </c>
       <c r="E18" t="n">
-        <v>9.295605793231871</v>
+        <v>181.4856369154794</v>
       </c>
       <c r="F18" t="n">
         <v>1.008058010600584</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7075693086092922</v>
+        <v>0.7075693086092923</v>
       </c>
       <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.317708333333333</v>
+      </c>
+      <c r="J18" t="n">
+        <v>7.468377976190475</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.893043154761904</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>7.468377976190475</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.317708333333333</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1142,25 +1669,52 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4.869422962522308</v>
+        <v>1856.122448979592</v>
       </c>
       <c r="D19" t="n">
-        <v>9.258661430056502</v>
+        <v>180.764342205865</v>
       </c>
       <c r="E19" t="n">
-        <v>9.183757342943331</v>
+        <v>179.3019290765126</v>
       </c>
       <c r="F19" t="n">
         <v>1.008156148329717</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7138236902316368</v>
+        <v>0.7138236902316369</v>
       </c>
       <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.126116071428571</v>
+      </c>
+      <c r="J19" t="n">
+        <v>7.894345238095237</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5.010230654761904</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>7.894345238095237</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.126116071428571</v>
+      </c>
+      <c r="S19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1172,25 +1726,52 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4.792088042831648</v>
+        <v>1826.643990929705</v>
       </c>
       <c r="D20" t="n">
-        <v>9.307441932399099</v>
+        <v>181.7167234420776</v>
       </c>
       <c r="E20" t="n">
-        <v>9.163551824848827</v>
+        <v>178.9074403899056</v>
       </c>
       <c r="F20" t="n">
         <v>1.015702438344931</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6951427245712607</v>
+        <v>0.6951427245712608</v>
       </c>
       <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.821056547619047</v>
+      </c>
+      <c r="J20" t="n">
+        <v>8.504464285714285</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5.162760416666666</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>8.504464285714285</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.821056547619047</v>
+      </c>
+      <c r="S20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1202,25 +1783,52 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4.792088042831648</v>
+        <v>1826.643990929705</v>
       </c>
       <c r="D21" t="n">
-        <v>9.307441932399099</v>
+        <v>181.7167234420776</v>
       </c>
       <c r="E21" t="n">
-        <v>9.163551824848827</v>
+        <v>178.9074403899056</v>
       </c>
       <c r="F21" t="n">
         <v>1.015702438344931</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6951427245712607</v>
+        <v>0.6951427245712608</v>
       </c>
       <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.821056547619047</v>
+      </c>
+      <c r="J21" t="n">
+        <v>8.504464285714285</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5.162760416666666</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>8.504464285714285</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.821056547619047</v>
+      </c>
+      <c r="S21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1231,7 +1839,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
       </c>
     </row>
     <row r="23">
@@ -1254,6 +1862,38 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/measurements/25/Filled_2D_sections/sagittal/week25_sagittal_Batch_Allmarks.xlsx
+++ b/measurements/25/Filled_2D_sections/sagittal/week25_sagittal_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1899,4 +2105,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week25_sagittal_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sagittal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1921.938775510204</v>
+      </c>
+      <c r="D10" t="n">
+        <v>51.75084798482319</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1826.643990929705</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1998.639455782313</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>196.5325342899277</v>
+      </c>
+      <c r="D11" t="n">
+        <v>14.95266237025871</v>
+      </c>
+      <c r="E11" t="n">
+        <v>180.764342205865</v>
+      </c>
+      <c r="F11" t="n">
+        <v>222.5453489735013</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.049308870627409</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.05341893619296763</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.005186653428375</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.170106223619049</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.63451665261748</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.08670226044788122</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.494717103946296</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.7138236902316369</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis0_s00_idx0138.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis0_s01_idx0138.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis0_s02_idx0139.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis0_s03_idx0140.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis0_s04_idx0140.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis0_s05_idx0141.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis0_s06_idx0142.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis0_s07_idx0143.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis0_s08_idx0143.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis0_s09_idx0144.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis0_s10_idx0145.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis0_s11_idx0146.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis0_s12_idx0146.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis0_s13_idx0147.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis0_s14_idx0148.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis0_s15_idx0149.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis0_s16_idx0149.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis0_s17_idx0150.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis0_s18_idx0151.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis0_s19_idx0151.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.4701623459816273</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.4701623459816272</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.489360484929593</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.4893604849295928</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>6</v>
+      </c>
+      <c r="C48" t="n">
+        <v>15.76946924603175</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.3327932675405332</v>
+      </c>
+      <c r="E48" t="n">
+        <v>15.11346726190476</v>
+      </c>
+      <c r="F48" t="n">
+        <v>15.99516369047619</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>27</v>
+      </c>
+      <c r="C49" t="n">
+        <v>6.822709986772486</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.625108985921317</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3.528645833333333</v>
+      </c>
+      <c r="F49" t="n">
+        <v>8.504464285714285</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>13</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1.939102564102564</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.5570451564020514</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.290922619047619</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.126860119047619</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>